--- a/utils/monday_sprint_sprint_2023-11.xlsx
+++ b/utils/monday_sprint_sprint_2023-11.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="152">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>18985</t>
+    <t>4101730301</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>07/03/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>01/06/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -117,10 +117,13 @@
     <t>23/03/2023</t>
   </si>
   <si>
+    <t>31/05/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>18631</t>
+    <t>4199872712</t>
   </si>
   <si>
     <t>Novo relatório - Relatório de Custos por Nota Fiscal</t>
@@ -129,7 +132,10 @@
     <t>24/03/2023</t>
   </si>
   <si>
-    <t>19387</t>
+    <t>21/05/2023</t>
+  </si>
+  <si>
+    <t>4271671869</t>
   </si>
   <si>
     <t>Fechar automaticamente após o final de cada turno da ajustagem.</t>
@@ -138,10 +144,13 @@
     <t>06/04/2023</t>
   </si>
   <si>
+    <t>03/06/2023</t>
+  </si>
+  <si>
     <t>Abril</t>
   </si>
   <si>
-    <t>19378</t>
+    <t>4273122982</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -150,13 +159,13 @@
     <t>Impressão de etiquetas - Sistema de Expedição</t>
   </si>
   <si>
+    <t>23/04/2023</t>
+  </si>
+  <si>
     <t>Em Análise</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>19927</t>
+    <t>4426806507</t>
   </si>
   <si>
     <t>Layout de tela para o gestão a vista da desmoldagem</t>
@@ -168,6 +177,9 @@
     <t>Maio</t>
   </si>
   <si>
+    <t>4436645067</t>
+  </si>
+  <si>
     <t>Layout de tela para o gestão a vista da desmoldagem - Tela de gestão a vista</t>
   </si>
   <si>
@@ -192,7 +204,10 @@
     <t>22/05/2023</t>
   </si>
   <si>
-    <t>18941</t>
+    <t>04/06/2023</t>
+  </si>
+  <si>
+    <t>4360648041</t>
   </si>
   <si>
     <t>Produtivo em horas - Lead Time em horas Part. 1</t>
@@ -201,10 +216,16 @@
     <t>24/04/2023</t>
   </si>
   <si>
+    <t>4512715549</t>
+  </si>
+  <si>
     <t>Produtivo em horas - Lead Time em horas Part. 2</t>
   </si>
   <si>
-    <t>20149</t>
+    <t>30/05/2023</t>
+  </si>
+  <si>
+    <t>4503911047</t>
   </si>
   <si>
     <t>Atribuição de justificativa para programação de sequencias sem data de entrega</t>
@@ -216,40 +237,52 @@
     <t>Semana 3</t>
   </si>
   <si>
+    <t>4504336688</t>
+  </si>
+  <si>
     <t>Contador de produção diária  para gestão a vista da desmoldagem</t>
   </si>
   <si>
-    <t>20220</t>
+    <t>4503676957</t>
   </si>
   <si>
     <t>Banco de Dados - Planilha ERP</t>
   </si>
   <si>
-    <t>20381</t>
+    <t>4505046735</t>
   </si>
   <si>
     <t>Tabela Lead Time - Qlik</t>
   </si>
   <si>
-    <t>19181</t>
+    <t>4511808468</t>
   </si>
   <si>
     <t>Novo processo de OTFs de Serviços/Ferramentais - PARTE 2</t>
   </si>
   <si>
-    <t>20305</t>
+    <t>28/05/2023</t>
+  </si>
+  <si>
+    <t>4503606757</t>
   </si>
   <si>
     <t>Falta critério no CPP</t>
   </si>
   <si>
-    <t>20214</t>
+    <t>24/05/2023</t>
+  </si>
+  <si>
+    <t>4503688628</t>
   </si>
   <si>
     <t>AVISO DE RX E DESMOLDAGEM E ACIARIA NO CPP</t>
   </si>
   <si>
-    <t>20087</t>
+    <t>23/05/2023</t>
+  </si>
+  <si>
+    <t>4441111941</t>
   </si>
   <si>
     <t>Consulta Estoque Por Área por Modelo</t>
@@ -258,22 +291,25 @@
     <t>09/05/2023</t>
   </si>
   <si>
+    <t>29/05/2023</t>
+  </si>
+  <si>
     <t>4514582744</t>
   </si>
   <si>
-    <t>20051</t>
+    <t>4503724973</t>
   </si>
   <si>
     <t>Avaliação de distúrbios</t>
   </si>
   <si>
-    <t>18614</t>
+    <t>4511689352</t>
   </si>
   <si>
     <t>Alteração apontamento de solda - Menu principal</t>
   </si>
   <si>
-    <t>19908</t>
+    <t>4472046528</t>
   </si>
   <si>
     <t>SERVIÇOS PENDENTES (acessar os serviços pendentes, legar os serviços executados, descrever os trabalhos realizados e confirmar o serviço)</t>
@@ -285,43 +321,58 @@
     <t>4514582934</t>
   </si>
   <si>
+    <t>4511745882</t>
+  </si>
+  <si>
     <t>Criar estrutura de tabelas</t>
   </si>
   <si>
+    <t>4511745977</t>
+  </si>
+  <si>
     <t>Criar Tema e menu principal</t>
   </si>
   <si>
+    <t>4511746068</t>
+  </si>
+  <si>
     <t>Baixar ordem de serviço programadas (Preventivas) Funcionários</t>
   </si>
   <si>
+    <t>4511746151</t>
+  </si>
+  <si>
     <t>Consultar Método</t>
   </si>
   <si>
-    <t>20247</t>
+    <t>25/05/2023</t>
+  </si>
+  <si>
+    <t>4503644599</t>
   </si>
   <si>
     <t>Melhoria de Relatório Aciaria</t>
   </si>
   <si>
-    <t>19910</t>
+    <t>4503795978</t>
   </si>
   <si>
     <t>Mudança na abertura de OS</t>
   </si>
   <si>
-    <t>20280</t>
+    <t>4503864905</t>
   </si>
   <si>
     <t>Melhoria lançamento notas fiscais</t>
   </si>
   <si>
-    <t>20096</t>
+    <t>4503706213</t>
   </si>
   <si>
     <t>Melhoria lançamento fiscal</t>
   </si>
   <si>
-    <t>20340</t>
+    <t>4505057625</t>
   </si>
   <si>
     <t>Mudança na tela de manutenção preventiva e inclusão de aberturas automáticas de SS</t>
@@ -333,7 +384,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-11</t>
+    <t>Mar/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -403,6 +454,9 @@
   </si>
   <si>
     <t>Fazendo</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -975,7 +1029,7 @@
         <v>33</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -984,7 +1038,7 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>28</v>
@@ -992,7 +1046,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1004,10 +1058,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>32</v>
@@ -1019,10 +1073,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1031,7 +1085,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1039,7 +1093,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1051,10 +1105,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>32</v>
@@ -1066,10 +1120,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1081,27 +1135,27 @@
         <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1113,27 +1167,27 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1145,10 +1199,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>32</v>
@@ -1160,10 +1214,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1175,12 +1229,12 @@
         <v>27</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1192,10 +1246,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>32</v>
@@ -1207,10 +1261,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1219,33 +1273,33 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>21</v>
@@ -1254,10 +1308,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1266,15 +1320,15 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1286,10 +1340,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>32</v>
@@ -1301,10 +1355,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1313,15 +1367,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1333,25 +1387,25 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1360,15 +1414,15 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1380,10 +1434,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>32</v>
@@ -1395,10 +1449,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1407,15 +1461,15 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1427,10 +1481,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>32</v>
@@ -1442,10 +1496,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1454,15 +1508,15 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1474,10 +1528,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>32</v>
@@ -1489,10 +1543,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1501,15 +1555,15 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1521,10 +1575,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>32</v>
@@ -1536,10 +1590,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1548,15 +1602,15 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1568,10 +1622,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>32</v>
@@ -1583,10 +1637,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1595,15 +1649,15 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1615,10 +1669,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>32</v>
@@ -1630,10 +1684,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1642,15 +1696,15 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1662,10 +1716,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>32</v>
@@ -1677,10 +1731,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1689,15 +1743,15 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1709,10 +1763,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>32</v>
@@ -1724,10 +1778,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1736,33 +1790,33 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O19" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>21</v>
@@ -1771,10 +1825,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1783,15 +1837,15 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1803,10 +1857,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>32</v>
@@ -1818,10 +1872,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1830,15 +1884,15 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1850,10 +1904,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>32</v>
@@ -1865,10 +1919,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1877,15 +1931,15 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1897,10 +1951,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>32</v>
@@ -1912,7 +1966,7 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>24</v>
@@ -1924,33 +1978,33 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>21</v>
@@ -1959,10 +2013,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -1971,15 +2025,15 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -1991,10 +2045,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>32</v>
@@ -2006,10 +2060,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2018,15 +2072,15 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2038,10 +2092,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>32</v>
@@ -2053,10 +2107,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2065,15 +2119,15 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2085,10 +2139,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>32</v>
@@ -2100,10 +2154,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2112,15 +2166,15 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2132,10 +2186,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>32</v>
@@ -2147,10 +2201,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2159,15 +2213,15 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2179,10 +2233,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>32</v>
@@ -2194,10 +2248,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2206,15 +2260,15 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2226,10 +2280,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>32</v>
@@ -2241,10 +2295,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2253,15 +2307,15 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2273,10 +2327,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>32</v>
@@ -2288,10 +2342,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2300,15 +2354,15 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2320,10 +2374,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>32</v>
@@ -2335,10 +2389,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2347,15 +2401,15 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2367,10 +2421,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>32</v>
@@ -2382,10 +2436,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2394,10 +2448,10 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2413,23 +2467,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2437,16 +2491,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2457,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>19.84</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2465,7 +2519,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2478,7 +2532,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2486,7 +2540,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2517,12 +2571,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="B2">
         <v>32</v>
@@ -2536,7 +2590,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2546,25 +2600,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2581,13 +2635,13 @@
         <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2602,12 +2656,12 @@
         <v>27</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -2622,19 +2676,19 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M11" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -2651,59 +2705,59 @@
         <v>27</v>
       </c>
       <c r="J12" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="Q12">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>34</v>
+        <v>147</v>
       </c>
       <c r="Q13">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2711,7 +2765,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2719,7 +2773,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2727,7 +2781,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -2735,10 +2789,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2746,7 +2800,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2754,142 +2808,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>1184</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
